--- a/src/data/High BLDC Gear Motor Price List 2026 14-02-26.xlsx
+++ b/src/data/High BLDC Gear Motor Price List 2026 14-02-26.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Haruj\gear-motor-app\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B978044B-A731-4838-9B4F-D0FF20202468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53316D68-CD03-4DC8-A620-FAFA6A624EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15765" xr2:uid="{065F6792-2FE2-4149-9BCA-9C0092E1C3E3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{065F6792-2FE2-4149-9BCA-9C0092E1C3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$263</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$D$296</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="371">
   <si>
     <t>Complete Set</t>
   </si>
@@ -4636,6 +4636,487 @@
       </rPr>
       <t>mm , Keyway.</t>
     </r>
+  </si>
+  <si>
+    <t>Z5BLD90-24GU-30S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-24GU-15S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-24GU-20S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-36GU-15S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-36GU-20S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-36GU-30S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-48GU-15S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-48GU-20S</t>
+  </si>
+  <si>
+    <t>Z5BLD90-48GU-30S</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 24VDC , Rate speed 1500 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 36VDC , Rate speed 1500 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 48VDC , Rate speed 1500 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 24VDC , Rate speed 2000 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 24VDC , Rate speed 3000 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 36VDC , Rate speed 2000 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 36VDC , Rate speed 3000 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 48VDC , Rate speed 2000 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>90W Brushless DC Motor , 48VDC , Rate speed 3000 rpm , IP20. Frame size 90mm.</t>
+  </si>
+  <si>
+    <t>5GU3KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU3.6KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU5KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:5 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU6KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:6 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU7.5KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:7.5 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU9KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:9 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU12.5KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU15KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU18KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU25KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU30KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:30 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU36KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:36 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU50KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:50 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU60KB</t>
+  </si>
+  <si>
+    <t>90mm gearbox, speed ratio 1:60 , Output shaft Dia. 15mm</t>
+  </si>
+  <si>
+    <t>5GU75KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU90KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU100KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU120KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU150KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU180KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>5GU200KB</t>
+  </si>
+  <si>
+    <r>
+      <t>90mm gearbox, speed ratio 1:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , Output shaft Dia. 15mm</t>
+    </r>
+  </si>
+  <si>
+    <t>ZBLD.C20-120L2R</t>
+  </si>
+  <si>
+    <t>Driver 24VDC , Brake function, RS485 Communication, CanOpen.</t>
+  </si>
+  <si>
+    <t>ZDRV.C20-200L-DR</t>
+  </si>
+  <si>
+    <t>ZBLD.C20-400LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver 240VDC With Display &amp; RS485 Communication. </t>
   </si>
 </sst>
 </file>
@@ -5081,6 +5562,42 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5140,42 +5657,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6071,25 +6552,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E3E70B-4089-46C0-AD37-31F889D31244}">
-  <dimension ref="A1:XFD390"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:XFD423"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="78.28515625" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="50.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="78.26953125" customWidth="1"/>
+    <col min="3" max="3" width="31.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:4" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -6103,125 +6584,125 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+    <row r="3" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="27"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="39"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="26"/>
       <c r="B4" s="8"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="28"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="40"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="26"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="28"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="40"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="26"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="28"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="40"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="26"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="28"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="40"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="26"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="28"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="40"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="26"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="28"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="40"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="26"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="28"/>
-    </row>
-    <row r="11" spans="1:4" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="40"/>
+    </row>
+    <row r="11" spans="1:4" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="29"/>
-    </row>
-    <row r="12" spans="1:4" ht="195" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-    </row>
-    <row r="13" spans="1:4" ht="74.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-    </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="C11" s="38"/>
+      <c r="D11" s="41"/>
+    </row>
+    <row r="12" spans="1:4" ht="195" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="44"/>
+    </row>
+    <row r="13" spans="1:4" ht="74.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+    </row>
+    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-    </row>
-    <row r="15" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="42" t="s">
+      <c r="C14" s="49"/>
+      <c r="D14" s="50"/>
+    </row>
+    <row r="15" spans="1:4" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="46"/>
+      <c r="B15" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="44"/>
-    </row>
-    <row r="16" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="42" t="s">
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="46"/>
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="44"/>
-    </row>
-    <row r="17" spans="1:4" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
-      <c r="B17" s="42" t="s">
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+    </row>
+    <row r="17" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="46"/>
+      <c r="B17" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="24"/>
+    </row>
+    <row r="18" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="46"/>
       <c r="B18" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
     </row>
-    <row r="19" spans="1:4" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35"/>
-      <c r="B19" s="39" t="s">
+    <row r="19" spans="1:4" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="47"/>
+      <c r="B19" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="41"/>
-    </row>
-    <row r="20" spans="1:4" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="1:4" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="11" t="s">
         <v>1</v>
       </c>
@@ -6235,15 +6716,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="15" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:4" s="15" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="23"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>92</v>
       </c>
@@ -6257,7 +6738,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
         <v>93</v>
       </c>
@@ -6271,7 +6752,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
         <v>17</v>
       </c>
@@ -6285,7 +6766,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>94</v>
       </c>
@@ -6299,7 +6780,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>154</v>
       </c>
@@ -6313,7 +6794,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
         <v>155</v>
       </c>
@@ -6327,7 +6808,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>156</v>
       </c>
@@ -6341,7 +6822,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>157</v>
       </c>
@@ -6355,7 +6836,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>210</v>
       </c>
@@ -6369,7 +6850,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>210</v>
       </c>
@@ -6383,7 +6864,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
         <v>210</v>
       </c>
@@ -6397,7 +6878,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>210</v>
       </c>
@@ -6411,7 +6892,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="14" t="s">
         <v>158</v>
       </c>
@@ -6425,7 +6906,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
         <v>159</v>
       </c>
@@ -6436,7 +6917,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
         <v>160</v>
       </c>
@@ -6447,7 +6928,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>161</v>
       </c>
@@ -6458,7 +6939,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>162</v>
       </c>
@@ -6469,7 +6950,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>19</v>
       </c>
@@ -6483,7 +6964,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
         <v>216</v>
       </c>
@@ -6497,7 +6978,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>217</v>
       </c>
@@ -6511,7 +6992,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
         <v>218</v>
       </c>
@@ -6525,7 +7006,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="14" t="s">
         <v>219</v>
       </c>
@@ -6539,7 +7020,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>220</v>
       </c>
@@ -6553,7 +7034,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
         <v>226</v>
       </c>
@@ -6567,7 +7048,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="14" t="s">
         <v>227</v>
       </c>
@@ -6581,7 +7062,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
         <v>228</v>
       </c>
@@ -6595,7 +7076,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="14" t="s">
         <v>229</v>
       </c>
@@ -6609,7 +7090,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
         <v>230</v>
       </c>
@@ -6623,7 +7104,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
         <v>231</v>
       </c>
@@ -6637,7 +7118,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
         <v>232</v>
       </c>
@@ -6651,7 +7132,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="14" t="s">
         <v>233</v>
       </c>
@@ -6665,14 +7146,14 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="14"/>
       <c r="B53" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="14" t="s">
         <v>21</v>
       </c>
@@ -6686,7 +7167,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="14" t="s">
         <v>214</v>
       </c>
@@ -6700,14 +7181,14 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="14"/>
       <c r="B56" t="s">
         <v>23</v>
       </c>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="14" t="s">
         <v>24</v>
       </c>
@@ -6721,7 +7202,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="14" t="s">
         <v>212</v>
       </c>
@@ -6735,14 +7216,14 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="14"/>
       <c r="B59" t="s">
         <v>25</v>
       </c>
       <c r="D59" s="4"/>
     </row>
-    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="14" t="s">
         <v>14</v>
       </c>
@@ -6756,7 +7237,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="14" t="s">
         <v>15</v>
       </c>
@@ -6770,15 +7251,15 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="21" t="s">
+    <row r="62" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="23"/>
-    </row>
-    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="35"/>
+    </row>
+    <row r="63" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="14" t="s">
         <v>98</v>
       </c>
@@ -6792,7 +7273,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="14" t="s">
         <v>99</v>
       </c>
@@ -6806,7 +7287,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="65" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="14" t="s">
         <v>31</v>
       </c>
@@ -6820,7 +7301,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="66" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="14" t="s">
         <v>100</v>
       </c>
@@ -6834,7 +7315,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="67" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="14" t="s">
         <v>33</v>
       </c>
@@ -6848,7 +7329,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="68" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="14" t="s">
         <v>71</v>
       </c>
@@ -6862,7 +7343,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="69" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="14" t="s">
         <v>72</v>
       </c>
@@ -6876,7 +7357,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="70" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="14" t="s">
         <v>73</v>
       </c>
@@ -6890,7 +7371,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="71" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="14"/>
       <c r="B71" t="s">
         <v>22</v>
@@ -6898,7 +7379,7 @@
       <c r="C71" s="2"/>
       <c r="D71" s="4"/>
     </row>
-    <row r="72" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="14" t="s">
         <v>34</v>
       </c>
@@ -6912,7 +7393,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="73" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="14" t="s">
         <v>78</v>
       </c>
@@ -6926,7 +7407,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="74" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="14"/>
       <c r="B74" t="s">
         <v>23</v>
@@ -6934,7 +7415,7 @@
       <c r="C74" s="2"/>
       <c r="D74" s="4"/>
     </row>
-    <row r="75" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="14" t="s">
         <v>35</v>
       </c>
@@ -6948,7 +7429,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="76" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="14" t="s">
         <v>80</v>
       </c>
@@ -6962,7 +7443,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="77" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="14"/>
       <c r="B77" t="s">
         <v>25</v>
@@ -6970,7 +7451,7 @@
       <c r="C77" s="2"/>
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="1:16384" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16384" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="14" t="s">
         <v>14</v>
       </c>
@@ -6984,7 +7465,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="79" spans="1:16384" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16384" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="14" t="s">
         <v>15</v>
       </c>
@@ -19283,15 +19764,15 @@
       <c r="XFC79" s="2"/>
       <c r="XFD79" s="4"/>
     </row>
-    <row r="80" spans="1:16384" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="21" t="s">
+    <row r="80" spans="1:16384" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="23"/>
-    </row>
-    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B80" s="34"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="35"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="14" t="s">
         <v>104</v>
       </c>
@@ -19305,7 +19786,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="14" t="s">
         <v>105</v>
       </c>
@@ -19319,7 +19800,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="14" t="s">
         <v>39</v>
       </c>
@@ -19333,7 +19814,7 @@
         <v>2690</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="14" t="s">
         <v>106</v>
       </c>
@@ -19347,7 +19828,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="14" t="s">
         <v>168</v>
       </c>
@@ -19361,7 +19842,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="14" t="s">
         <v>169</v>
       </c>
@@ -19375,7 +19856,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="14" t="s">
         <v>170</v>
       </c>
@@ -19389,7 +19870,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="14" t="s">
         <v>171</v>
       </c>
@@ -19403,7 +19884,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="14" t="s">
         <v>172</v>
       </c>
@@ -19417,7 +19898,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="14" t="s">
         <v>178</v>
       </c>
@@ -19428,7 +19909,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="14" t="s">
         <v>179</v>
       </c>
@@ -19439,7 +19920,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="14" t="s">
         <v>180</v>
       </c>
@@ -19450,7 +19931,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="14" t="s">
         <v>181</v>
       </c>
@@ -19461,7 +19942,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="14" t="s">
         <v>48</v>
       </c>
@@ -19475,7 +19956,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="14" t="s">
         <v>83</v>
       </c>
@@ -19489,7 +19970,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="14" t="s">
         <v>84</v>
       </c>
@@ -19503,7 +19984,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="14" t="s">
         <v>82</v>
       </c>
@@ -19517,14 +19998,14 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="14"/>
       <c r="B98" t="s">
         <v>22</v>
       </c>
       <c r="D98" s="4"/>
     </row>
-    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="14" t="s">
         <v>47</v>
       </c>
@@ -19538,7 +20019,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="14" t="s">
         <v>88</v>
       </c>
@@ -19552,14 +20033,14 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="14"/>
       <c r="B101" t="s">
         <v>23</v>
       </c>
       <c r="D101" s="4"/>
     </row>
-    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="14" t="s">
         <v>46</v>
       </c>
@@ -19573,7 +20054,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="14" t="s">
         <v>90</v>
       </c>
@@ -19587,14 +20068,14 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="14"/>
       <c r="B104" t="s">
         <v>25</v>
       </c>
       <c r="D104" s="4"/>
     </row>
-    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="14" t="s">
         <v>14</v>
       </c>
@@ -19608,7 +20089,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="14" t="s">
         <v>15</v>
       </c>
@@ -19622,948 +20103,987 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="21" t="s">
+    <row r="107" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B107" s="22"/>
-      <c r="C107" s="22"/>
-      <c r="D107" s="23"/>
-    </row>
-    <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B107" s="34"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="35"/>
+    </row>
+    <row r="108" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="14" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="B108" t="s">
-        <v>111</v>
+        <v>315</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D108" s="4">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="14" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>318</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D109" s="4">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="14" t="s">
-        <v>49</v>
+        <v>306</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>319</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D110" s="4">
-        <v>2750</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="14" t="s">
-        <v>109</v>
+        <v>309</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D111" s="4">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="14" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="B112" t="s">
-        <v>142</v>
+        <v>320</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D112" s="4">
-        <v>3490</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="14" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="B113" t="s">
-        <v>141</v>
+        <v>321</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D113" s="4">
-        <v>3490</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="14" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="B114" t="s">
-        <v>60</v>
+        <v>317</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D114" s="4">
-        <v>3490</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="14" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="B115" t="s">
-        <v>140</v>
+        <v>322</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D115" s="4">
-        <v>3490</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="14" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="B116" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D116" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="14" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="B117" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D117" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="14" t="s">
-        <v>248</v>
+        <v>326</v>
       </c>
       <c r="B118" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="14" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="B119" t="s">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D119" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="14" t="s">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="B120" t="s">
-        <v>258</v>
+        <v>331</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="14" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
       <c r="B121" t="s">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D121" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="14" t="s">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="B122" t="s">
-        <v>260</v>
+        <v>335</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D122" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="14" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
       <c r="B123" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D123" s="4">
-        <v>3240</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="14" t="s">
-        <v>48</v>
+        <v>338</v>
       </c>
       <c r="B124" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D124" s="4">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="14" t="s">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="B125" t="s">
-        <v>85</v>
+        <v>341</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D125" s="4">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="14" t="s">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="B126" t="s">
-        <v>113</v>
+        <v>343</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D126" s="4">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="14" t="s">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="B127" t="s">
-        <v>87</v>
+        <v>345</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D127" s="4">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="14"/>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A128" s="14" t="s">
+        <v>346</v>
+      </c>
       <c r="B128" t="s">
-        <v>22</v>
-      </c>
-      <c r="D128" s="4"/>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D128" s="4">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="14" t="s">
-        <v>47</v>
+        <v>348</v>
       </c>
       <c r="B129" t="s">
-        <v>44</v>
+        <v>349</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D129" s="4">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="14" t="s">
-        <v>88</v>
+        <v>350</v>
       </c>
       <c r="B130" t="s">
-        <v>89</v>
+        <v>351</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D130" s="4">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="14"/>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A131" s="14" t="s">
+        <v>352</v>
+      </c>
       <c r="B131" t="s">
-        <v>23</v>
-      </c>
-      <c r="D131" s="4"/>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D131" s="4">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="14" t="s">
-        <v>46</v>
+        <v>354</v>
       </c>
       <c r="B132" t="s">
-        <v>45</v>
+        <v>355</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D132" s="4">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="14" t="s">
-        <v>90</v>
+        <v>356</v>
       </c>
       <c r="B133" t="s">
-        <v>91</v>
+        <v>357</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D133" s="4">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="14"/>
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A134" s="14" t="s">
+        <v>358</v>
+      </c>
       <c r="B134" t="s">
-        <v>25</v>
-      </c>
-      <c r="D134" s="4"/>
-    </row>
-    <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D134" s="4">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="14" t="s">
-        <v>14</v>
+        <v>360</v>
       </c>
       <c r="B135" t="s">
-        <v>27</v>
+        <v>361</v>
       </c>
       <c r="C135" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D135" s="4">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A136" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="B136" t="s">
+        <v>363</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136" s="4">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A137" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="B137" t="s">
+        <v>365</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" s="4">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A138" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B138" t="s">
+        <v>367</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D135" s="4">
-        <v>5390</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>28</v>
-      </c>
-      <c r="C136" s="2" t="s">
+      <c r="D138" s="4">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B139" t="s">
+        <v>370</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D136" s="4">
-        <v>5460</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B137" s="22"/>
-      <c r="C137" s="22"/>
-      <c r="D137" s="23"/>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B138" t="s">
+      <c r="D139" s="4">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B140" t="s">
+        <v>367</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D140" s="4">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A141" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B141" t="s">
         <v>111</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D138" s="4">
-        <v>2960</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B139" t="s">
-        <v>112</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D139" s="4">
-        <v>2960</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B140" t="s">
-        <v>50</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D140" s="4">
-        <v>2960</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="B141" t="s">
-        <v>110</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D141" s="4">
-        <v>3090</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="14" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D142" s="4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="14" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D143" s="4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="14" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="B144" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D144" s="4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="14" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="B145" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D145" s="4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="14" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="B146" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="C146" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" s="4">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A147" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B147" t="s">
+        <v>60</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" s="4">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A148" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="B148" t="s">
+        <v>140</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" s="4">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A149" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B149" t="s">
+        <v>254</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B147" t="s">
-        <v>192</v>
-      </c>
-      <c r="D147" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B148" t="s">
-        <v>193</v>
-      </c>
-      <c r="D148" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B149" t="s">
-        <v>194</v>
-      </c>
       <c r="D149" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="14" t="s">
-        <v>190</v>
+        <v>247</v>
       </c>
       <c r="B150" t="s">
-        <v>195</v>
+        <v>255</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="D150" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="14" t="s">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="B151" t="s">
-        <v>55</v>
+        <v>256</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D151" s="4">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="14" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="B152" t="s">
-        <v>132</v>
+        <v>257</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D152" s="4">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="14" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="B153" t="s">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D153" s="4">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="14" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
       <c r="B154" t="s">
-        <v>130</v>
+        <v>259</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D154" s="4">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="14"/>
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A155" s="14" t="s">
+        <v>252</v>
+      </c>
       <c r="B155" t="s">
-        <v>22</v>
-      </c>
-      <c r="D155" s="4"/>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D155" s="4">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="14" t="s">
-        <v>53</v>
+        <v>253</v>
       </c>
       <c r="B156" t="s">
-        <v>56</v>
+        <v>261</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D156" s="4">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="14" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="B157" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D157" s="4">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="14"/>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A158" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="B158" t="s">
-        <v>23</v>
-      </c>
-      <c r="D158" s="4"/>
-    </row>
-    <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" s="4">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="14" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="B159" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D159" s="4">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="14" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="B160" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D160" s="4">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="14"/>
       <c r="B161" t="s">
+        <v>22</v>
+      </c>
+      <c r="D161" s="4"/>
+    </row>
+    <row r="162" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A162" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B162" t="s">
+        <v>44</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D162" s="4">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A163" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B163" t="s">
+        <v>89</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D163" s="4">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A164" s="14"/>
+      <c r="B164" t="s">
+        <v>23</v>
+      </c>
+      <c r="D164" s="4"/>
+    </row>
+    <row r="165" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A165" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B165" t="s">
+        <v>45</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="4">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A166" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B166" t="s">
+        <v>91</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D166" s="4">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A167" s="14"/>
+      <c r="B167" t="s">
         <v>25</v>
       </c>
-      <c r="D161" s="4"/>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="14" t="s">
+      <c r="D167" s="4"/>
+    </row>
+    <row r="168" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A168" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B168" t="s">
         <v>27</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C168" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D168" s="4">
         <v>5390</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="14" t="s">
+    <row r="169" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B169" t="s">
         <v>28</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C169" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D163" s="4">
+      <c r="D169" s="4">
         <v>5460</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B164" s="22"/>
-      <c r="C164" s="22"/>
-      <c r="D164" s="23"/>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B165" t="s">
-        <v>142</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D165" s="4">
-        <v>3790</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B166" t="s">
-        <v>141</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D166" s="4">
-        <v>3790</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B167" t="s">
-        <v>60</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D167" s="4">
-        <v>3790</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B168" t="s">
-        <v>140</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D168" s="4">
-        <v>3890</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B169" t="s">
-        <v>151</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D169" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B170" t="s">
-        <v>152</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D170" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B170" s="34"/>
+      <c r="C170" s="34"/>
+      <c r="D170" s="35"/>
+    </row>
+    <row r="171" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="14" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="B171" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D171" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="14" t="s">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="B172" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D172" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="14" t="s">
-        <v>266</v>
+        <v>51</v>
       </c>
       <c r="B173" t="s">
-        <v>274</v>
+        <v>50</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D173" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="14" t="s">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="B174" t="s">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D174" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="14" t="s">
-        <v>268</v>
+        <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>276</v>
+        <v>142</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D175" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="14" t="s">
-        <v>269</v>
+        <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D176" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="14" t="s">
-        <v>270</v>
+        <v>184</v>
       </c>
       <c r="B177" t="s">
-        <v>278</v>
+        <v>60</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D177" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="14" t="s">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="B178" t="s">
-        <v>279</v>
+        <v>140</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D178" s="4">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="14" t="s">
-        <v>272</v>
+        <v>186</v>
       </c>
       <c r="B179" t="s">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>4</v>
@@ -20572,1370 +21092,1787 @@
         <v>3640</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="14" t="s">
-        <v>273</v>
+        <v>187</v>
       </c>
       <c r="B180" t="s">
-        <v>281</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>4</v>
+        <v>192</v>
       </c>
       <c r="D180" s="4">
         <v>3640</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" t="s">
+        <v>193</v>
+      </c>
+      <c r="D181" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A182" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B182" t="s">
+        <v>194</v>
+      </c>
+      <c r="D182" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A183" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" t="s">
+        <v>195</v>
+      </c>
+      <c r="D183" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A184" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B184" t="s">
         <v>55</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D181" s="4">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B182" t="s">
-        <v>132</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D182" s="4">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B183" t="s">
-        <v>143</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D183" s="4">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B184" t="s">
-        <v>130</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D184" s="4">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A185" s="14"/>
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A185" s="14" t="s">
+        <v>127</v>
+      </c>
       <c r="B185" t="s">
-        <v>22</v>
-      </c>
-      <c r="D185" s="4"/>
-    </row>
-    <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D185" s="4">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="14" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="B186" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D186" s="4">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="14" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B187" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D187" s="4">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="14"/>
       <c r="B188" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D188" s="4"/>
     </row>
-    <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B189" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D189" s="4">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B190" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D190" s="4">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="14"/>
       <c r="B191" t="s">
+        <v>23</v>
+      </c>
+      <c r="D191" s="4"/>
+    </row>
+    <row r="192" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A192" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B192" t="s">
+        <v>57</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D192" s="4">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A193" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B193" t="s">
+        <v>136</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D193" s="4">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A194" s="14"/>
+      <c r="B194" t="s">
         <v>25</v>
       </c>
-      <c r="D191" s="4"/>
-    </row>
-    <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="14" t="s">
+      <c r="D194" s="4"/>
+    </row>
+    <row r="195" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A195" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B195" t="s">
         <v>27</v>
       </c>
-      <c r="C192" s="2" t="s">
+      <c r="C195" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D192" s="4">
+      <c r="D195" s="4">
         <v>5390</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="14" t="s">
+    <row r="196" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B196" t="s">
         <v>28</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="C196" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D193" s="4">
+      <c r="D196" s="4">
         <v>5460</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="21" t="s">
+    <row r="197" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A197" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B194" s="22"/>
-      <c r="C194" s="22"/>
-      <c r="D194" s="23"/>
-    </row>
-    <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="B197" s="34"/>
+      <c r="C197" s="34"/>
+      <c r="D197" s="35"/>
+    </row>
+    <row r="198" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A198" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B198" t="s">
         <v>142</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D195" s="4">
-        <v>4380</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B196" t="s">
-        <v>141</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D196" s="4">
-        <v>4380</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B197" t="s">
-        <v>60</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D197" s="4">
-        <v>4380</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B198" t="s">
-        <v>140</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D198" s="4">
-        <v>4490</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="14" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="B199" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="C199" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D199" s="4">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A200" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B200" t="s">
+        <v>60</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D200" s="4">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A201" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B201" t="s">
+        <v>140</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" s="4">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A202" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B202" t="s">
+        <v>151</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A203" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B203" t="s">
+        <v>152</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D203" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A204" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B204" t="s">
+        <v>70</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D204" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A205" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B205" t="s">
+        <v>153</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D205" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A206" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="B206" t="s">
+        <v>274</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="4">
-        <v>3590</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B200" t="s">
-        <v>122</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D200" s="4">
-        <v>3590</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A201" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B201" t="s">
-        <v>123</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D201" s="4">
-        <v>3590</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B202" t="s">
-        <v>124</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D202" s="4">
-        <v>3590</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="14"/>
-      <c r="B203" t="s">
-        <v>22</v>
-      </c>
-      <c r="D203" s="4"/>
-    </row>
-    <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B204" t="s">
-        <v>66</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D204" s="4">
-        <v>3960</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B205" t="s">
-        <v>120</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D205" s="4">
-        <v>3960</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="14"/>
-      <c r="B206" t="s">
-        <v>23</v>
-      </c>
-      <c r="D206" s="4"/>
-    </row>
-    <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D206" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="14" t="s">
-        <v>62</v>
+        <v>267</v>
       </c>
       <c r="B207" t="s">
-        <v>67</v>
+        <v>275</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D207" s="4">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="14" t="s">
-        <v>117</v>
+        <v>268</v>
       </c>
       <c r="B208" t="s">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D208" s="4">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A209" s="14"/>
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A209" s="14" t="s">
+        <v>269</v>
+      </c>
       <c r="B209" t="s">
+        <v>277</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D209" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A210" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B210" t="s">
+        <v>278</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D210" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A211" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="B211" t="s">
+        <v>279</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D211" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A212" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B212" t="s">
+        <v>280</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D212" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A213" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="B213" t="s">
+        <v>281</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D213" s="4">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A214" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B214" t="s">
+        <v>55</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D214" s="4">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A215" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B215" t="s">
+        <v>132</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D215" s="4">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A216" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B216" t="s">
+        <v>143</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D216" s="4">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A217" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B217" t="s">
+        <v>130</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D217" s="4">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A218" s="14"/>
+      <c r="B218" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218" s="4"/>
+    </row>
+    <row r="219" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A219" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B219" t="s">
+        <v>56</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D219" s="4">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A220" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B220" t="s">
+        <v>134</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D220" s="4">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A221" s="14"/>
+      <c r="B221" t="s">
+        <v>23</v>
+      </c>
+      <c r="D221" s="4"/>
+    </row>
+    <row r="222" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A222" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B222" t="s">
+        <v>57</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D222" s="4">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A223" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B223" t="s">
+        <v>136</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D223" s="4">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A224" s="14"/>
+      <c r="B224" t="s">
         <v>25</v>
       </c>
-      <c r="D209" s="4"/>
-    </row>
-    <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A210" s="14" t="s">
+      <c r="D224" s="4"/>
+    </row>
+    <row r="225" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A225" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B225" t="s">
         <v>27</v>
       </c>
-      <c r="C210" s="2" t="s">
+      <c r="C225" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D210" s="4">
+      <c r="D225" s="4">
         <v>5390</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="14" t="s">
+    <row r="226" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B226" t="s">
         <v>28</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="C226" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D211" s="4">
+      <c r="D226" s="4">
         <v>5460</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B212" s="22"/>
-      <c r="C212" s="22"/>
-      <c r="D212" s="23"/>
-    </row>
-    <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A213" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B213" t="s">
-        <v>151</v>
-      </c>
-      <c r="C213" s="2" t="s">
+    <row r="227" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A227" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B227" s="34"/>
+      <c r="C227" s="34"/>
+      <c r="D227" s="35"/>
+    </row>
+    <row r="228" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A228" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B228" t="s">
+        <v>142</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D213" s="4">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="B214" t="s">
-        <v>152</v>
-      </c>
-      <c r="C214" s="2" t="s">
+      <c r="D228" s="4">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A229" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B229" t="s">
+        <v>141</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D214" s="4">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A215" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B215" t="s">
-        <v>70</v>
-      </c>
-      <c r="C215" s="2" t="s">
+      <c r="D229" s="4">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A230" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B230" t="s">
+        <v>60</v>
+      </c>
+      <c r="C230" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D215" s="4">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A216" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B216" t="s">
-        <v>153</v>
-      </c>
-      <c r="C216" s="2" t="s">
+      <c r="D230" s="4">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A231" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B231" t="s">
+        <v>140</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D216" s="4">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A217" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="B217" t="s">
-        <v>151</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D217" s="4">
-        <v>5230</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A218" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B218" t="s">
-        <v>152</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D218" s="4">
-        <v>5230</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A219" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="B219" t="s">
-        <v>70</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D219" s="4">
-        <v>5230</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B220" t="s">
-        <v>153</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D220" s="4">
-        <v>5230</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="B221" t="s">
-        <v>283</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D221" s="4">
-        <v>7840</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A222" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B222" t="s">
-        <v>288</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D222" s="4">
-        <v>7840</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A223" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="B223" t="s">
-        <v>289</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D223" s="4">
-        <v>7840</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A224" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="B224" t="s">
-        <v>287</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D224" s="4">
-        <v>7840</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A225" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B225" t="s">
-        <v>298</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D225" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A226" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="B226" t="s">
-        <v>299</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D226" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A227" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B227" t="s">
-        <v>300</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D227" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A228" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="B228" t="s">
-        <v>301</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D228" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A229" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="B229" t="s">
-        <v>302</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D229" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A230" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B230" t="s">
-        <v>303</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D230" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A231" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="B231" t="s">
-        <v>304</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="D231" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="14" t="s">
-        <v>297</v>
+        <v>64</v>
       </c>
       <c r="B232" t="s">
-        <v>305</v>
+        <v>65</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D232" s="4">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="14" t="s">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="B233" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D233" s="4">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="14" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="B234" t="s">
-        <v>205</v>
+        <v>123</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="D234" s="4">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="14" t="s">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="B235" t="s">
-        <v>206</v>
+        <v>124</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="D235" s="4">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="14" t="s">
-        <v>204</v>
-      </c>
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A236" s="14"/>
       <c r="B236" t="s">
-        <v>207</v>
-      </c>
-      <c r="D236" s="4">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="D236" s="4"/>
+    </row>
+    <row r="237" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="14" t="s">
-        <v>203</v>
+        <v>63</v>
       </c>
       <c r="B237" t="s">
-        <v>208</v>
+        <v>66</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="D237" s="4">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="14" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="B238" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D238" s="4">
-        <v>3860</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A239" s="14" t="s">
-        <v>121</v>
-      </c>
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A239" s="14"/>
       <c r="B239" t="s">
-        <v>122</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D239" s="4">
-        <v>3860</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="D239" s="4"/>
+    </row>
+    <row r="240" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="14" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="B240" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D240" s="4">
-        <v>3860</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="14" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B241" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D241" s="4">
-        <v>3860</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="14"/>
       <c r="B242" t="s">
+        <v>25</v>
+      </c>
+      <c r="D242" s="4"/>
+    </row>
+    <row r="243" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A243" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" t="s">
+        <v>27</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D243" s="4">
+        <v>5390</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A244" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B244" t="s">
+        <v>28</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D244" s="4">
+        <v>5460</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B245" s="34"/>
+      <c r="C245" s="34"/>
+      <c r="D245" s="35"/>
+    </row>
+    <row r="246" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A246" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B246" t="s">
+        <v>151</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D246" s="4">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A247" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B247" t="s">
+        <v>152</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D247" s="4">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A248" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B248" t="s">
+        <v>70</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D248" s="4">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A249" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B249" t="s">
+        <v>153</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D249" s="4">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A250" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B250" t="s">
+        <v>151</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D250" s="4">
+        <v>5230</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A251" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B251" t="s">
+        <v>152</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D251" s="4">
+        <v>5230</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A252" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B252" t="s">
+        <v>70</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D252" s="4">
+        <v>5230</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A253" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B253" t="s">
+        <v>153</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D253" s="4">
+        <v>5230</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A254" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B254" t="s">
+        <v>283</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D254" s="4">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A255" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B255" t="s">
+        <v>288</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D255" s="4">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A256" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B256" t="s">
+        <v>289</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D256" s="4">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A257" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B257" t="s">
+        <v>287</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D257" s="4">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A258" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B258" t="s">
+        <v>298</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D258" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A259" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B259" t="s">
+        <v>299</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D259" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A260" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B260" t="s">
+        <v>300</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D260" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A261" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B261" t="s">
+        <v>301</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D261" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A262" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B262" t="s">
+        <v>302</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D262" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A263" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B263" t="s">
+        <v>303</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D263" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A264" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B264" t="s">
+        <v>304</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D264" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A265" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B265" t="s">
+        <v>305</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D265" s="4">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A266" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B266" t="s">
+        <v>209</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D266" s="4">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A267" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B267" t="s">
+        <v>205</v>
+      </c>
+      <c r="D267" s="4">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A268" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B268" t="s">
+        <v>206</v>
+      </c>
+      <c r="D268" s="4">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A269" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B269" t="s">
+        <v>207</v>
+      </c>
+      <c r="D269" s="4">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A270" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B270" t="s">
+        <v>208</v>
+      </c>
+      <c r="D270" s="4">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A271" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B271" t="s">
+        <v>65</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D271" s="4">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A272" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B272" t="s">
+        <v>122</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D272" s="4">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A273" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B273" t="s">
+        <v>123</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D273" s="4">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A274" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B274" t="s">
+        <v>124</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D274" s="4">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A275" s="14"/>
+      <c r="B275" t="s">
         <v>22</v>
       </c>
-      <c r="D242" s="4"/>
-    </row>
-    <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A243" s="14" t="s">
+      <c r="D275" s="4"/>
+    </row>
+    <row r="276" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A276" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B276" t="s">
         <v>66</v>
       </c>
-      <c r="C243" s="2" t="s">
+      <c r="C276" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="4">
+      <c r="D276" s="4">
         <v>4260</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A244" s="14" t="s">
+    <row r="277" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A277" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B277" t="s">
         <v>120</v>
       </c>
-      <c r="C244" s="2" t="s">
+      <c r="C277" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="4">
+      <c r="D277" s="4">
         <v>4260</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A245" s="14"/>
-      <c r="B245" t="s">
+    <row r="278" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A278" s="14"/>
+      <c r="B278" t="s">
         <v>23</v>
       </c>
-      <c r="D245" s="4"/>
-    </row>
-    <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A246" s="14" t="s">
+      <c r="D278" s="4"/>
+    </row>
+    <row r="279" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A279" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B279" t="s">
         <v>67</v>
       </c>
-      <c r="C246" s="2" t="s">
+      <c r="C279" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="4">
+      <c r="D279" s="4">
         <v>4420</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A247" s="14" t="s">
+    <row r="280" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A280" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B280" t="s">
         <v>118</v>
       </c>
-      <c r="C247" s="2" t="s">
+      <c r="C280" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="4">
+      <c r="D280" s="4">
         <v>4420</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A248" s="14"/>
-      <c r="B248" t="s">
+    <row r="281" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A281" s="14"/>
+      <c r="B281" t="s">
         <v>25</v>
       </c>
-      <c r="D248" s="4"/>
-    </row>
-    <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A249" s="14" t="s">
+      <c r="D281" s="4"/>
+    </row>
+    <row r="282" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A282" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B282" t="s">
         <v>27</v>
       </c>
-      <c r="C249" s="2" t="s">
+      <c r="C282" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D249" s="4">
+      <c r="D282" s="4">
         <v>5390</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="14" t="s">
+    <row r="283" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A283" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B283" t="s">
         <v>28</v>
       </c>
-      <c r="C250" s="2" t="s">
+      <c r="C283" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D250" s="4">
+      <c r="D283" s="4">
         <v>5460</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" s="13"/>
-      <c r="B251" s="12"/>
-      <c r="D251" s="4"/>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" s="13"/>
-      <c r="D252" s="4"/>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="13"/>
-      <c r="D253" s="4"/>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" s="13"/>
-      <c r="D254" s="4"/>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" s="13"/>
-      <c r="B255" s="19"/>
-      <c r="D255" s="4"/>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" s="13"/>
-      <c r="B256" s="19"/>
-      <c r="D256" s="4"/>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" s="13"/>
-      <c r="B257" s="19"/>
-      <c r="D257" s="4"/>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="13"/>
-      <c r="D258" s="4"/>
-    </row>
-    <row r="259" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="13"/>
-      <c r="B259" s="19"/>
-      <c r="D259" s="4"/>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A260" s="13"/>
-      <c r="B260" s="19"/>
-      <c r="D260" s="4"/>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" s="13"/>
-      <c r="B261" s="19"/>
-      <c r="D261" s="4"/>
-    </row>
-    <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A262" s="14"/>
-      <c r="D262" s="4"/>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A263" s="13"/>
-      <c r="D263" s="4"/>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D264" s="4"/>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D265" s="4"/>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D266" s="4"/>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D267" s="4"/>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D268" s="4"/>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D269" s="4"/>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D270" s="4"/>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D271" s="4"/>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D272" s="4"/>
-    </row>
-    <row r="273" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D273" s="4"/>
-    </row>
-    <row r="274" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D274" s="4"/>
-    </row>
-    <row r="275" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D275" s="4"/>
-    </row>
-    <row r="276" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D276" s="4"/>
-    </row>
-    <row r="277" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D277" s="4"/>
-    </row>
-    <row r="278" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D278" s="4"/>
-    </row>
-    <row r="279" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D279" s="4"/>
-    </row>
-    <row r="280" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D280" s="4"/>
-    </row>
-    <row r="281" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D281" s="4"/>
-    </row>
-    <row r="282" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D282" s="4"/>
-    </row>
-    <row r="283" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D283" s="4"/>
-    </row>
-    <row r="284" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" s="13"/>
+      <c r="B284" s="12"/>
       <c r="D284" s="4"/>
     </row>
-    <row r="285" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" s="13"/>
       <c r="D285" s="4"/>
     </row>
-    <row r="286" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" s="13"/>
       <c r="D286" s="4"/>
     </row>
-    <row r="287" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" s="13"/>
       <c r="D287" s="4"/>
     </row>
-    <row r="288" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" s="13"/>
+      <c r="B288" s="31"/>
       <c r="D288" s="4"/>
     </row>
-    <row r="289" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" s="13"/>
+      <c r="B289" s="31"/>
       <c r="D289" s="4"/>
     </row>
-    <row r="290" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A290" s="13"/>
+      <c r="B290" s="31"/>
       <c r="D290" s="4"/>
     </row>
-    <row r="291" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A291" s="13"/>
       <c r="D291" s="4"/>
     </row>
-    <row r="292" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A292" s="13"/>
+      <c r="B292" s="31"/>
       <c r="D292" s="4"/>
     </row>
-    <row r="293" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A293" s="13"/>
+      <c r="B293" s="31"/>
       <c r="D293" s="4"/>
     </row>
-    <row r="294" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A294" s="13"/>
+      <c r="B294" s="31"/>
       <c r="D294" s="4"/>
     </row>
-    <row r="295" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A295" s="14"/>
       <c r="D295" s="4"/>
     </row>
-    <row r="296" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A296" s="13"/>
       <c r="D296" s="4"/>
     </row>
-    <row r="297" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D297" s="4"/>
     </row>
-    <row r="298" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D298" s="4"/>
     </row>
-    <row r="299" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D299" s="4"/>
     </row>
-    <row r="300" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D300" s="4"/>
     </row>
-    <row r="301" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D301" s="4"/>
     </row>
-    <row r="302" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D302" s="4"/>
     </row>
-    <row r="303" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D303" s="4"/>
     </row>
-    <row r="304" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D304" s="4"/>
     </row>
-    <row r="305" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D305" s="4"/>
     </row>
-    <row r="306" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D306" s="4"/>
     </row>
-    <row r="307" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D307" s="4"/>
     </row>
-    <row r="308" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D308" s="4"/>
     </row>
-    <row r="309" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D309" s="4"/>
     </row>
-    <row r="310" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D310" s="4"/>
     </row>
-    <row r="311" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D311" s="4"/>
     </row>
-    <row r="312" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D312" s="4"/>
     </row>
-    <row r="313" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D313" s="4"/>
     </row>
-    <row r="314" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D314" s="4"/>
     </row>
-    <row r="315" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D315" s="4"/>
     </row>
-    <row r="316" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D316" s="4"/>
     </row>
-    <row r="317" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D317" s="4"/>
     </row>
-    <row r="318" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D318" s="4"/>
     </row>
-    <row r="319" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D319" s="4"/>
     </row>
-    <row r="320" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D320" s="4"/>
     </row>
-    <row r="321" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D321" s="4"/>
     </row>
-    <row r="322" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D322" s="4"/>
     </row>
-    <row r="323" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D323" s="4"/>
     </row>
-    <row r="324" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D324" s="4"/>
     </row>
-    <row r="325" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D325" s="4"/>
     </row>
-    <row r="326" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D326" s="4"/>
     </row>
-    <row r="327" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D327" s="4"/>
     </row>
-    <row r="328" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D328" s="4"/>
     </row>
-    <row r="329" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D329" s="4"/>
     </row>
-    <row r="330" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D330" s="4"/>
     </row>
-    <row r="331" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D331" s="4"/>
     </row>
-    <row r="332" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D332" s="4"/>
     </row>
-    <row r="333" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D333" s="4"/>
     </row>
-    <row r="334" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D334" s="4"/>
     </row>
-    <row r="335" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D335" s="4"/>
     </row>
-    <row r="336" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D336" s="4"/>
     </row>
-    <row r="337" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D337" s="4"/>
     </row>
-    <row r="338" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D338" s="4"/>
     </row>
-    <row r="339" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D339" s="4"/>
     </row>
-    <row r="340" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D340" s="4"/>
     </row>
-    <row r="341" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D341" s="4"/>
     </row>
-    <row r="342" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D342" s="4"/>
     </row>
-    <row r="343" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D343" s="4"/>
     </row>
-    <row r="344" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D344" s="4"/>
     </row>
-    <row r="345" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D345" s="4"/>
     </row>
-    <row r="346" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D346" s="4"/>
     </row>
-    <row r="347" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D347" s="4"/>
     </row>
-    <row r="348" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D348" s="4"/>
     </row>
-    <row r="349" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D349" s="4"/>
     </row>
-    <row r="350" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D350" s="4"/>
     </row>
-    <row r="351" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D351" s="4"/>
     </row>
-    <row r="352" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D352" s="4"/>
     </row>
-    <row r="353" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D353" s="4"/>
     </row>
-    <row r="354" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D354" s="4"/>
     </row>
-    <row r="355" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D355" s="4"/>
     </row>
-    <row r="356" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D356" s="4"/>
     </row>
-    <row r="357" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D357" s="4"/>
     </row>
-    <row r="358" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D358" s="4"/>
     </row>
-    <row r="359" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D359" s="4"/>
     </row>
-    <row r="360" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D360" s="4"/>
     </row>
-    <row r="361" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D361" s="4"/>
     </row>
-    <row r="362" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D362" s="4"/>
     </row>
-    <row r="363" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D363" s="4"/>
     </row>
-    <row r="364" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D364" s="4"/>
     </row>
-    <row r="365" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D365" s="4"/>
     </row>
-    <row r="366" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D366" s="4"/>
     </row>
-    <row r="367" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D367" s="4"/>
     </row>
-    <row r="368" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D368" s="4"/>
     </row>
-    <row r="369" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D369" s="4"/>
     </row>
-    <row r="370" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D370" s="4"/>
     </row>
-    <row r="371" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D371" s="4"/>
     </row>
-    <row r="372" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D372" s="4"/>
     </row>
-    <row r="373" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D373" s="4"/>
     </row>
-    <row r="374" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D374" s="4"/>
     </row>
-    <row r="375" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D375" s="4"/>
     </row>
-    <row r="376" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D376" s="4"/>
     </row>
-    <row r="377" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D377" s="4"/>
     </row>
-    <row r="378" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D378" s="4"/>
     </row>
-    <row r="379" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D379" s="4"/>
     </row>
-    <row r="380" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D380" s="4"/>
     </row>
-    <row r="381" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D381" s="4"/>
     </row>
-    <row r="382" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D382" s="4"/>
     </row>
-    <row r="383" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D383" s="4"/>
     </row>
-    <row r="384" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D384" s="4"/>
     </row>
-    <row r="385" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D385" s="4"/>
     </row>
-    <row r="386" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D386" s="4"/>
     </row>
-    <row r="387" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D387" s="4"/>
     </row>
-    <row r="388" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D388" s="4"/>
     </row>
-    <row r="389" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D389" s="4"/>
     </row>
-    <row r="390" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D390" s="4"/>
+    </row>
+    <row r="391" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D391" s="4"/>
+    </row>
+    <row r="392" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D392" s="4"/>
+    </row>
+    <row r="393" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D393" s="4"/>
+    </row>
+    <row r="394" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D394" s="4"/>
+    </row>
+    <row r="395" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D395" s="4"/>
+    </row>
+    <row r="396" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D396" s="4"/>
+    </row>
+    <row r="397" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D397" s="4"/>
+    </row>
+    <row r="398" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D398" s="4"/>
+    </row>
+    <row r="399" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D399" s="4"/>
+    </row>
+    <row r="400" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D400" s="4"/>
+    </row>
+    <row r="401" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D401" s="4"/>
+    </row>
+    <row r="402" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D402" s="4"/>
+    </row>
+    <row r="403" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D403" s="4"/>
+    </row>
+    <row r="404" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D404" s="4"/>
+    </row>
+    <row r="405" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D405" s="4"/>
+    </row>
+    <row r="406" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D406" s="4"/>
+    </row>
+    <row r="407" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D407" s="4"/>
+    </row>
+    <row r="408" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D408" s="4"/>
+    </row>
+    <row r="409" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D409" s="4"/>
+    </row>
+    <row r="410" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D410" s="4"/>
+    </row>
+    <row r="411" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D411" s="4"/>
+    </row>
+    <row r="412" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D412" s="4"/>
+    </row>
+    <row r="413" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D413" s="4"/>
+    </row>
+    <row r="414" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D414" s="4"/>
+    </row>
+    <row r="415" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D415" s="4"/>
+    </row>
+    <row r="416" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D416" s="4"/>
+    </row>
+    <row r="417" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D417" s="4"/>
+    </row>
+    <row r="418" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D418" s="4"/>
+    </row>
+    <row r="419" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D419" s="4"/>
+    </row>
+    <row r="420" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D420" s="4"/>
+    </row>
+    <row r="421" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D421" s="4"/>
+    </row>
+    <row r="422" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D422" s="4"/>
+    </row>
+    <row r="423" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D423" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A3:A13"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B255:B257"/>
-    <mergeCell ref="B259:B261"/>
+    <mergeCell ref="B288:B290"/>
+    <mergeCell ref="B292:B294"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A137:D137"/>
+    <mergeCell ref="A170:D170"/>
     <mergeCell ref="C3:C11"/>
     <mergeCell ref="D3:D11"/>
-    <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A194:D194"/>
-    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A197:D197"/>
+    <mergeCell ref="A227:D227"/>
+    <mergeCell ref="A245:D245"/>
     <mergeCell ref="A107:D107"/>
     <mergeCell ref="A80:D80"/>
     <mergeCell ref="A62:D62"/>
@@ -21943,6 +22880,12 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A3:A13"/>
+    <mergeCell ref="B13:D13"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -21951,10 +22894,10 @@
   <rowBreaks count="6" manualBreakCount="6">
     <brk id="19" max="3" man="1"/>
     <brk id="106" max="3" man="1"/>
-    <brk id="136" max="3" man="1"/>
-    <brk id="163" max="16383" man="1"/>
-    <brk id="193" max="16383" man="1"/>
-    <brk id="211" max="16383" man="1"/>
+    <brk id="169" max="3" man="1"/>
+    <brk id="196" max="16383" man="1"/>
+    <brk id="226" max="16383" man="1"/>
+    <brk id="244" max="16383" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
